--- a/data/trans_orig/IQ39A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según el número de horas que trabaja habitualmente a la semana</t>
+          <t>Adulto según el número de horas que trabaja habitualmente a la semana (tasa de respuesta: 97,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,81; 39,34</t>
+          <t>35,72; 39,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,71; 39,67</t>
+          <t>35,77; 39,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,1; 39,45</t>
+          <t>36,01; 39,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,86; 38,29</t>
+          <t>35,9; 38,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,63; 39,83</t>
+          <t>36,39; 39,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,32; 40,62</t>
+          <t>37,28; 40,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,02; 39,25</t>
+          <t>35,67; 39,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,68; 38,16</t>
+          <t>35,82; 38,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,61; 39,12</t>
+          <t>36,67; 39,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,09; 39,73</t>
+          <t>37,23; 39,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,51; 38,92</t>
+          <t>36,47; 38,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,24; 37,88</t>
+          <t>36,17; 37,96</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,79; 39,27</t>
+          <t>36,82; 39,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,96; 39,09</t>
+          <t>37,0; 39,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,58; 37,88</t>
+          <t>34,52; 37,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,32; 38,16</t>
+          <t>35,16; 38,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,32; 38,23</t>
+          <t>35,22; 38,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,61; 37,95</t>
+          <t>34,51; 38,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,05; 39,4</t>
+          <t>36,24; 39,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,17; 37,23</t>
+          <t>34,03; 37,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,39; 38,44</t>
+          <t>36,43; 38,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,04; 38,2</t>
+          <t>36,08; 38,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,09; 38,38</t>
+          <t>36,03; 38,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,43; 37,47</t>
+          <t>35,37; 37,48</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,82; 45,0</t>
+          <t>41,93; 45,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,87; 43,78</t>
+          <t>39,91; 43,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,76; 43,59</t>
+          <t>38,45; 43,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,64; 44,48</t>
+          <t>37,06; 44,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,17; 43,7</t>
+          <t>40,39; 43,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,88; 45,16</t>
+          <t>39,93; 45,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,01; 41,99</t>
+          <t>37,05; 41,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,45; 47,29</t>
+          <t>39,45; 46,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,28; 43,75</t>
+          <t>41,36; 43,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40,46; 43,77</t>
+          <t>40,47; 43,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38,46; 41,96</t>
+          <t>38,41; 42,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39,13; 44,59</t>
+          <t>39,11; 44,44</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,9; 42,68</t>
+          <t>39,92; 42,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,78; 39,06</t>
+          <t>35,65; 38,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,63; 40,43</t>
+          <t>36,76; 40,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,22; 40,0</t>
+          <t>36,9; 39,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,41; 41,34</t>
+          <t>38,54; 41,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,11; 39,6</t>
+          <t>35,85; 39,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,62; 40,02</t>
+          <t>36,47; 39,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,73; 40,73</t>
+          <t>37,49; 40,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,67; 41,7</t>
+          <t>39,6; 41,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,4; 38,86</t>
+          <t>36,43; 38,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,22; 39,78</t>
+          <t>37,2; 39,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,83; 39,95</t>
+          <t>37,78; 39,92</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,06; 38,1</t>
+          <t>31,91; 37,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,28; 34,79</t>
+          <t>29,41; 34,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27,47; 33,33</t>
+          <t>27,77; 33,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,32; 36,23</t>
+          <t>32,08; 36,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,61; 39,24</t>
+          <t>35,66; 39,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,07; 35,65</t>
+          <t>30,3; 36,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,02; 37,15</t>
+          <t>30,91; 37,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,34; 37,79</t>
+          <t>34,32; 37,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,71; 38,04</t>
+          <t>34,73; 38,11</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,66; 34,54</t>
+          <t>30,56; 34,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,57; 34,8</t>
+          <t>30,38; 34,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,29; 36,64</t>
+          <t>34,16; 36,73</t>
         </is>
       </c>
     </row>
@@ -1416,22 +1416,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,3; 42,51</t>
+          <t>34,22; 42,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30,39; 42,76</t>
+          <t>29,81; 42,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,39; 38,86</t>
+          <t>20,2; 38,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,99; 40,0</t>
+          <t>10,79; 40,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,35; 44,67</t>
+          <t>33,87; 44,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40,0; 46,74</t>
+          <t>40,0; 46,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,61; 39,95</t>
+          <t>25,43; 39,94</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34,84; 43,01</t>
+          <t>34,86; 43,18</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,06; 47,55</t>
+          <t>23,2; 47,35</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,25; 41,88</t>
+          <t>21,86; 41,59</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,55; 40,25</t>
+          <t>38,57; 40,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36,54; 38,37</t>
+          <t>36,62; 38,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,0; 37,93</t>
+          <t>36,14; 38,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36,51; 38,11</t>
+          <t>36,58; 38,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>38,13; 39,72</t>
+          <t>38,24; 39,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,86; 38,83</t>
+          <t>36,9; 38,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,76; 38,72</t>
+          <t>36,64; 38,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,11; 38,75</t>
+          <t>37,15; 38,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,59; 39,76</t>
+          <t>38,62; 39,71</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37,05; 38,35</t>
+          <t>37,02; 38,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36,73; 38,01</t>
+          <t>36,69; 37,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,17; 38,27</t>
+          <t>37,12; 38,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ39A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Clase-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,72; 39,45</t>
+          <t>36,04; 39,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,77; 39,65</t>
+          <t>35,82; 39,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,01; 39,57</t>
+          <t>35,99; 39,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,9; 38,41</t>
+          <t>35,73; 38,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,39; 39,65</t>
+          <t>36,53; 39,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,28; 40,53</t>
+          <t>37,27; 40,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,67; 39,18</t>
+          <t>35,93; 39,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,82; 38,26</t>
+          <t>35,7; 38,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,67; 39,1</t>
+          <t>36,59; 39,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,23; 39,78</t>
+          <t>37,06; 39,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,47; 38,92</t>
+          <t>36,47; 38,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,17; 37,96</t>
+          <t>36,27; 37,96</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,82; 39,26</t>
+          <t>36,85; 39,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,0; 39,17</t>
+          <t>36,97; 39,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,52; 37,85</t>
+          <t>34,68; 37,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,16; 38,24</t>
+          <t>35,29; 38,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,22; 38,14</t>
+          <t>35,19; 38,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,51; 38,05</t>
+          <t>34,27; 38,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,24; 39,46</t>
+          <t>36,03; 39,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,03; 37,3</t>
+          <t>34,18; 37,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,43; 38,43</t>
+          <t>36,53; 38,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,08; 38,15</t>
+          <t>36,1; 38,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,03; 38,29</t>
+          <t>35,9; 38,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,37; 37,48</t>
+          <t>35,31; 37,45</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,93; 45,22</t>
+          <t>41,95; 45,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,91; 43,56</t>
+          <t>39,88; 43,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,45; 43,61</t>
+          <t>38,63; 43,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37,06; 44,18</t>
+          <t>36,79; 44,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,39; 43,66</t>
+          <t>40,15; 43,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,93; 45,42</t>
+          <t>39,88; 45,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,05; 41,95</t>
+          <t>37,18; 42,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,45; 46,78</t>
+          <t>39,53; 46,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,36; 43,77</t>
+          <t>41,51; 43,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40,47; 43,91</t>
+          <t>40,36; 43,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38,41; 42,04</t>
+          <t>38,55; 42,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39,11; 44,44</t>
+          <t>38,95; 44,52</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,92; 42,69</t>
+          <t>40,05; 42,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,65; 38,88</t>
+          <t>35,86; 39,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,76; 40,4</t>
+          <t>36,77; 40,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,9; 39,93</t>
+          <t>37,04; 39,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,54; 41,49</t>
+          <t>38,47; 41,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,85; 39,67</t>
+          <t>36,14; 39,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,47; 39,86</t>
+          <t>36,67; 40,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,49; 40,56</t>
+          <t>37,7; 40,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,6; 41,63</t>
+          <t>39,58; 41,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,43; 38,98</t>
+          <t>36,5; 38,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,2; 39,62</t>
+          <t>37,26; 39,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,78; 39,92</t>
+          <t>37,8; 39,83</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,91; 37,94</t>
+          <t>31,73; 37,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,41; 34,69</t>
+          <t>29,37; 34,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27,77; 33,14</t>
+          <t>27,82; 33,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,08; 36,17</t>
+          <t>32,37; 36,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,66; 39,12</t>
+          <t>35,64; 39,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,3; 36,12</t>
+          <t>29,85; 35,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,91; 37,26</t>
+          <t>31,54; 37,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,32; 37,74</t>
+          <t>34,41; 37,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,73; 38,11</t>
+          <t>34,65; 38,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,56; 34,63</t>
+          <t>30,32; 34,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,38; 34,66</t>
+          <t>30,42; 34,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,16; 36,73</t>
+          <t>34,1; 36,7</t>
         </is>
       </c>
     </row>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,22; 42,54</t>
+          <t>34,2; 42,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,81; 42,76</t>
+          <t>30,62; 42,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,2; 38,89</t>
+          <t>20,39; 39,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,87; 44,48</t>
+          <t>34,7; 44,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,43; 39,94</t>
+          <t>23,84; 39,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34,86; 43,18</t>
+          <t>35,54; 43,08</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,2; 47,35</t>
+          <t>22,56; 47,3</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,86; 41,59</t>
+          <t>22,53; 41,59</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,57; 40,24</t>
+          <t>38,67; 40,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36,62; 38,38</t>
+          <t>36,64; 38,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,14; 38,08</t>
+          <t>35,99; 37,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36,58; 38,14</t>
+          <t>36,52; 38,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>38,24; 39,72</t>
+          <t>38,17; 39,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,9; 38,84</t>
+          <t>36,94; 38,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,48</t>
+          <t>36,64; 38,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,15; 38,74</t>
+          <t>37,18; 38,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,62; 39,71</t>
+          <t>38,64; 39,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37,02; 38,35</t>
+          <t>37,05; 38,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36,69; 37,96</t>
+          <t>36,66; 37,99</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,12; 38,23</t>
+          <t>37,11; 38,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ39A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Clase-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38,17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38,99</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37,55</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37,11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>37,81</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>37,72</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>37,81</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37,18</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>38,17</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>38,99</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,55</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,11</t>
+          <t>37,16</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,14</t>
+          <t>37,13</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,04; 39,59</t>
+          <t>36,63; 39,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,82; 39,78</t>
+          <t>37,32; 40,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,99; 39,73</t>
+          <t>36,02; 39,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,73; 38,31</t>
+          <t>35,66; 38,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,53; 39,76</t>
+          <t>35,81; 39,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,27; 40,68</t>
+          <t>35,71; 39,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,93; 39,08</t>
+          <t>36,1; 39,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,7; 38,25</t>
+          <t>35,85; 38,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,59; 39,15</t>
+          <t>36,61; 39,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,06; 39,72</t>
+          <t>37,09; 39,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,47; 38,89</t>
+          <t>36,51; 38,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,27; 37,96</t>
+          <t>36,18; 37,92</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>36,87</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>36,36</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37,89</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>36,04</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>38,16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>38,11</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>36,44</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>37,11</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,87</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>36,36</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>37,89</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35,99</t>
+          <t>37,14</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36,54</t>
+          <t>36,6</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,85; 39,34</t>
+          <t>35,32; 38,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,97; 39,11</t>
+          <t>34,61; 37,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,68; 37,99</t>
+          <t>36,05; 39,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,29; 38,25</t>
+          <t>34,14; 37,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,19; 38,15</t>
+          <t>36,79; 39,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,27; 38,02</t>
+          <t>36,96; 39,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,03; 39,46</t>
+          <t>34,58; 37,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,18; 37,28</t>
+          <t>35,27; 38,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,53; 38,48</t>
+          <t>36,39; 38,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,1; 38,16</t>
+          <t>36,04; 38,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,9; 38,21</t>
+          <t>36,09; 38,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,31; 37,45</t>
+          <t>35,48; 37,52</t>
         </is>
       </c>
     </row>
@@ -928,49 +928,49 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>41,99</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42,58</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>39,86</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>43,01</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>43,34</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>41,72</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>41,02</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>40,01</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>41,99</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>40,34</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>42,58</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>39,86</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>42,51</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>42,58</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>42,11</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,37</t>
+          <t>41,69</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,95; 45,2</t>
+          <t>40,17; 43,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,88; 43,76</t>
+          <t>39,88; 45,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,63; 43,47</t>
+          <t>37,01; 41,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,79; 44,12</t>
+          <t>40,66; 47,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,15; 43,53</t>
+          <t>41,82; 45,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,88; 45,3</t>
+          <t>39,87; 43,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,18; 42,23</t>
+          <t>38,76; 43,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,53; 46,97</t>
+          <t>36,81; 45,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,51; 43,95</t>
+          <t>41,28; 43,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40,36; 43,77</t>
+          <t>40,46; 43,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38,55; 42,16</t>
+          <t>38,46; 41,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,95; 44,52</t>
+          <t>39,57; 44,75</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39,95</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37,84</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>38,35</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39,06</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>41,38</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>37,46</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>38,56</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38,58</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>39,95</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,84</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38,35</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,06</t>
+          <t>38,77</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,84</t>
+          <t>38,93</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,05; 42,81</t>
+          <t>38,41; 41,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,86; 39,11</t>
+          <t>36,11; 39,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,77; 40,4</t>
+          <t>36,62; 40,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,04; 39,93</t>
+          <t>37,68; 40,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,47; 41,43</t>
+          <t>39,9; 42,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,14; 39,95</t>
+          <t>35,78; 39,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,67; 40,07</t>
+          <t>36,63; 40,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,7; 40,56</t>
+          <t>37,58; 40,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,58; 41,58</t>
+          <t>39,67; 41,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,5; 38,9</t>
+          <t>36,4; 38,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,26; 39,75</t>
+          <t>37,22; 39,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,8; 39,83</t>
+          <t>37,97; 40,07</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>37,4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33,19</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>34,09</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>36,13</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>34,94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>32,15</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>30,81</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>34,42</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>37,4</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>33,19</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>34,09</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36,29</t>
+          <t>34,3</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35,49</t>
+          <t>35,29</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,73; 37,9</t>
+          <t>35,61; 39,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,37; 34,81</t>
+          <t>30,07; 35,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27,82; 33,24</t>
+          <t>31,02; 37,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,37; 36,27</t>
+          <t>34,17; 37,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,64; 39,02</t>
+          <t>32,06; 38,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,85; 35,59</t>
+          <t>29,28; 34,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,54; 37,48</t>
+          <t>27,47; 33,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,41; 37,69</t>
+          <t>32,08; 36,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,65; 38,08</t>
+          <t>34,71; 38,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,32; 34,42</t>
+          <t>30,66; 34,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,42; 34,61</t>
+          <t>30,57; 34,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,1; 36,7</t>
+          <t>34,01; 36,42</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>26,2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>40,82</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>42,45</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>43,39</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>38,58</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>37,88</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>30,3</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30,09</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>26,2</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>40,82</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>42,45</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>43,3</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,98</t>
+          <t>35,42</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,2; 42,72</t>
+          <t>7,0; 38,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30,62; 42,79</t>
+          <t>34,35; 44,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,39; 39,38</t>
+          <t>9,0; 60,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,79; 40,0</t>
+          <t>40,0; 47,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,0; 38,24</t>
+          <t>34,3; 42,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,7; 44,6</t>
+          <t>30,39; 42,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,0; 60,0</t>
+          <t>20,39; 38,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40,0; 46,68</t>
+          <t>9,8; 40,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,84; 39,9</t>
+          <t>25,61; 39,95</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35,54; 43,08</t>
+          <t>34,84; 43,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,56; 47,3</t>
+          <t>23,06; 47,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,53; 41,59</t>
+          <t>19,57; 41,51</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38,96</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>37,9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37,65</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>37,93</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>39,46</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>37,51</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>37,03</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>37,37</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38,96</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>37,9</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>37,65</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>37,93</t>
+          <t>37,41</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>37,67</t>
+          <t>37,69</t>
         </is>
       </c>
     </row>
@@ -1556,47 +1556,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,67; 40,31</t>
+          <t>38,13; 39,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,43</t>
+          <t>36,86; 38,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,99; 37,95</t>
+          <t>36,76; 38,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36,52; 38,15</t>
+          <t>37,16; 38,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>38,17; 39,66</t>
+          <t>38,55; 40,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,94; 38,92</t>
+          <t>36,54; 38,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,54</t>
+          <t>36,0; 37,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,18; 38,78</t>
+          <t>36,52; 38,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,64; 39,72</t>
+          <t>38,59; 39,76</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36,66; 37,99</t>
+          <t>36,73; 38,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,11; 38,21</t>
+          <t>37,2; 38,31</t>
         </is>
       </c>
     </row>
